--- a/docs/oc-regiones/pasajes-aereos-nacionales/nuble.xlsx
+++ b/docs/oc-regiones/pasajes-aereos-nacionales/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>96.66</v>
+        <v>95.84</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>71.84</v>
+        <v>71.47</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>495.22</v>
+        <v>492.68</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>288.97</v>
+        <v>285.94</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>318.03</v>
+        <v>316.29</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>409.58</v>
+        <v>407.34</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>612.04</v>
+        <v>614.0599999999999</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>445.12</v>
+        <v>452.8</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>152.71</v>
+        <v>155.35</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>384.09</v>
+        <v>390.72</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>114.77</v>
+        <v>116.76</v>
       </c>
     </row>
     <row r="13">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>99.26000000000001</v>
+        <v>99.11</v>
       </c>
     </row>
     <row r="14">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>367.72</v>
+        <v>367.43</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>147.46</v>
+        <v>145.33</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>355.96</v>
+        <v>358.29</v>
       </c>
     </row>
     <row r="17">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>411</v>
+        <v>420.99</v>
       </c>
     </row>
     <row r="18">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>719.55</v>
+        <v>741.37</v>
       </c>
     </row>
     <row r="19">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>161.14</v>
+        <v>160.98</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>85.01000000000001</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>315.67</v>
+        <v>313.95</v>
       </c>
     </row>
     <row r="22">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>83.75</v>
+        <v>84.08</v>
       </c>
     </row>
     <row r="23">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>89.05</v>
+        <v>90.52</v>
       </c>
     </row>
     <row r="24">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1224.6</v>
+        <v>1227.61</v>
       </c>
     </row>
     <row r="25">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>851.77</v>
+        <v>867.22</v>
       </c>
     </row>
     <row r="26">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>687.9</v>
+        <v>700.38</v>
       </c>
     </row>
     <row r="27">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>122.33</v>
+        <v>122.32</v>
       </c>
     </row>
     <row r="29">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>501.94</v>
+        <v>506.2</v>
       </c>
     </row>
     <row r="30">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>232.8</v>
+        <v>235.66</v>
       </c>
     </row>
     <row r="31">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>99.81999999999999</v>
+        <v>100.72</v>
       </c>
     </row>
     <row r="32">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>283.18</v>
+        <v>285</v>
       </c>
     </row>
     <row r="33">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>37.88</v>
+        <v>38.12</v>
       </c>
     </row>
     <row r="34">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>171.99</v>
+        <v>173.09</v>
       </c>
     </row>
     <row r="35">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>354.63</v>
+        <v>355.75</v>
       </c>
     </row>
     <row r="36">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>981.85</v>
+        <v>983.89</v>
       </c>
     </row>
     <row r="37">
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>258.93</v>
+        <v>261.83</v>
       </c>
     </row>
     <row r="38">
@@ -2769,13 +2769,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>161.23</v>
+        <v>160.52</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1049242-28-CM26</t>
+          <t>1049242-27-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2830,13 +2830,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>199.82</v>
+        <v>188.24</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4121-38-CM26</t>
+          <t>1049242-28-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2856,17 +2856,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>62.000.430-8</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>Secretaria Regional Ministerial de las Artes y el</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JETSMART</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>304.12</v>
+        <v>198.94</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1049242-27-CM26</t>
+          <t>1039043-44-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>62.000.430-8</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Secretaria Regional Ministerial de las Artes y el</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2952,13 +2952,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>189.07</v>
+        <v>267.92</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1039043-44-CM26</t>
+          <t>4121-38-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2978,17 +2978,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>269.1</v>
+        <v>302.78</v>
       </c>
     </row>
     <row r="43">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>109.88</v>
+        <v>111.74</v>
       </c>
     </row>
     <row r="44">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>570.8</v>
+        <v>580.45</v>
       </c>
     </row>
     <row r="45">
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>357.65</v>
+        <v>363.69</v>
       </c>
     </row>
     <row r="46">
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>151.42</v>
+        <v>148.86</v>
       </c>
     </row>
     <row r="47">
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>118.47</v>
+        <v>116.47</v>
       </c>
     </row>
     <row r="48">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>196.71</v>
+        <v>193.39</v>
       </c>
     </row>
     <row r="49">
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>196.71</v>
+        <v>193.92</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3841-79-CM26</t>
+          <t>3784-298-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3466,17 +3466,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.141.600-3</t>
+          <t>69.150.200-7</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PEMUCO</t>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3501,13 +3501,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>109.56</v>
+        <v>275.15</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3784-298-CM26</t>
+          <t>3841-79-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3527,17 +3527,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>69.141.600-3</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>I MUNICIPALIDAD DE PEMUCO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3562,7 +3562,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>278.98</v>
+        <v>108.06</v>
       </c>
     </row>
     <row r="52">
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>211.79</v>
+        <v>214.94</v>
       </c>
     </row>
     <row r="53">
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>273.52</v>
+        <v>275.41</v>
       </c>
     </row>
     <row r="54">
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>273.52</v>
+        <v>275.41</v>
       </c>
     </row>
     <row r="55">
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>352.72</v>
+        <v>355.15</v>
       </c>
     </row>
     <row r="56">
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>128.27</v>
+        <v>127.62</v>
       </c>
     </row>
     <row r="57">
@@ -3936,13 +3936,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>415.75</v>
+        <v>416.71</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4886-84-CM26</t>
+          <t>4886-82-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3997,13 +3997,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>129.49</v>
+        <v>259.57</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4886-82-CM26</t>
+          <t>4886-84-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>258.98</v>
+        <v>129.79</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4886-81-CM26</t>
+          <t>4886-80-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4119,13 +4119,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>392.11</v>
+        <v>320.2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4886-80-CM26</t>
+          <t>4886-81-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>319.46</v>
+        <v>393.01</v>
       </c>
     </row>
     <row r="62">
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>270.77</v>
+        <v>272.58</v>
       </c>
     </row>
     <row r="63">
@@ -4302,7 +4302,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>156.02</v>
+        <v>157.06</v>
       </c>
     </row>
     <row r="64">
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>538.58</v>
+        <v>536.88</v>
       </c>
     </row>
     <row r="65">
@@ -4424,13 +4424,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>415.47</v>
+        <v>414.57</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1016-60-CM26</t>
+          <t>1016-63-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4485,13 +4485,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>233.38</v>
+        <v>155.71</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1016-61-CM26</t>
+          <t>1016-65-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4546,13 +4546,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>206.17</v>
+        <v>131.27</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1016-62-CM26</t>
+          <t>1016-64-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4607,13 +4607,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>171.14</v>
+        <v>137.98</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1016-63-CM26</t>
+          <t>1016-62-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>156.02</v>
+        <v>170.8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1016-64-CM26</t>
+          <t>1016-61-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4729,13 +4729,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>138.26</v>
+        <v>205.76</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1016-65-CM26</t>
+          <t>1016-60-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>131.53</v>
+        <v>232.92</v>
       </c>
     </row>
     <row r="72">
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>119.6</v>
+        <v>118.9</v>
       </c>
     </row>
     <row r="73">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>111.32</v>
+        <v>109.53</v>
       </c>
     </row>
     <row r="74">
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>287.88</v>
+        <v>283.23</v>
       </c>
     </row>
     <row r="75">
@@ -5034,7 +5034,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>373.05</v>
+        <v>367.03</v>
       </c>
     </row>
     <row r="76">
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>274.39</v>
+        <v>269.99</v>
       </c>
     </row>
     <row r="77">
@@ -5156,7 +5156,251 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>397.76</v>
+        <v>400.42</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2705-1225-CM26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>60.911.006-6</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>JetSMART</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>58.17</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2705-1227-CM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>60.911.006-6</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>JetSMART</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>102.69</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1155683-107-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>178.78</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1049242-52-CM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>62.000.430-8</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>806.36</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/pasajes-aereos-nacionales/nuble.xlsx
+++ b/docs/oc-regiones/pasajes-aereos-nacionales/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1700-106-CM25</t>
+          <t>1173803-8-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>95.84</v>
+        <v>177.68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1700-107-CM25</t>
+          <t>1059240-23-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>71.47</v>
+        <v>219.38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2705-1649-CM25</t>
+          <t>1208103-34-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>492.68</v>
+        <v>467.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1016-111-CM25</t>
+          <t>1063487-17-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>285.94</v>
+        <v>106.51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1059240-73-CM25</t>
+          <t>1016-78-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>316.29</v>
+        <v>118.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1016-114-CM25</t>
+          <t>1049242-92-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.430-8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>407.34</v>
+        <v>449.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2705-1746-CM25</t>
+          <t>1043030-81-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>62.000.480-4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>614.0599999999999</v>
+        <v>423.01</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1063487-22-CM25</t>
+          <t>2705-1573-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>452.8</v>
+        <v>454.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1173803-28-CM25</t>
+          <t>1700-106-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>155.35</v>
+        <v>95.84</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1059240-78-CM25</t>
+          <t>1700-107-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>JETSMART</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>390.72</v>
+        <v>71.47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4886-225-CM25</t>
+          <t>2705-1649-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,22 +1139,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,18 +1179,18 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>116.76</v>
+        <v>492.68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1059240-85-SE25</t>
+          <t>1016-111-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2239-23-LP10</t>
+          <t>2239-16-LR23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1233,24 +1233,20 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>99.11</v>
+        <v>285.94</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1016-125-CM25</t>
+          <t>1059240-73-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1260,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1275,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1290,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1305,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>367.43</v>
+        <v>316.29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1059240-1-CM26</t>
+          <t>1016-114-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1321,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1336,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1366,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>145.33</v>
+        <v>407.34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1057509-954-CM26</t>
+          <t>2705-1746-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1382,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1397,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.607.001-0</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO HERMINDA MARTIN</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1412,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1427,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>358.29</v>
+        <v>614.0599999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1051765-41-CM26</t>
+          <t>1059240-78-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1443,27 +1439,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>62.000.570-3</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1473,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1488,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>420.99</v>
+        <v>390.72</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1057509-1306-CM26</t>
+          <t>1173803-28-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1504,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1519,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.607.001-0</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO HERMINDA MARTIN</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1549,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>741.37</v>
+        <v>155.35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1051765-107-CM26</t>
+          <t>1063487-22-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1565,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>62.000.570-3</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1595,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1610,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>160.98</v>
+        <v>452.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1063487-7-CM26</t>
+          <t>4886-225-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1626,27 +1622,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>53.312.479-8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1656,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1671,43 +1667,43 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>84.40000000000001</v>
+        <v>116.76</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1051765-111-CM26</t>
+          <t>1059240-85-SE25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2239-16-LR23</t>
+          <t>2239-23-LP10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>62.000.570-3</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1725,20 +1721,24 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>313.95</v>
+        <v>99.11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1059240-6-CM26</t>
+          <t>1016-125-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1793,13 +1793,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>84.08</v>
+        <v>367.43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1059240-8-CM26</t>
+          <t>1059240-1-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1854,13 +1854,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>90.52</v>
+        <v>145.33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1353712-9-CM26</t>
+          <t>1057509-954-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1870,27 +1870,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.981.150-K</t>
+          <t>61.607.001-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE ÑUBLE SERPAT</t>
+          <t>HOSPITAL CLINICO HERMINDA MARTIN</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JETSMART</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1227.61</v>
+        <v>358.29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1059240-10-CM26</t>
+          <t>1051765-41-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1931,27 +1931,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>62.000.570-3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>Dirección Regional de Ñuble</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>867.22</v>
+        <v>420.99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1700-19-CM26</t>
+          <t>1057509-1306-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2007,12 +2007,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.607.001-0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>HOSPITAL CLINICO HERMINDA MARTIN</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2037,13 +2037,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>700.38</v>
+        <v>741.37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1700-20-CM26</t>
+          <t>1051765-107-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2053,27 +2053,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>62.000.570-3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>Dirección Regional de Ñuble</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>69.13</v>
+        <v>160.98</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1700-21-CM26</t>
+          <t>1063487-7-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2159,13 +2159,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>122.32</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1208103-10-CM26</t>
+          <t>1051765-111-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>62.000.570-3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>Dirección Regional de Ñuble</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2220,13 +2220,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>506.2</v>
+        <v>313.95</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1208103-12-CM26</t>
+          <t>1059240-6-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2236,27 +2236,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>235.66</v>
+        <v>84.08</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1016-15-CM26</t>
+          <t>1059240-8-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2312,12 +2312,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2327,12 +2327,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>JETSMART</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>100.72</v>
+        <v>90.52</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1016-16-CM26</t>
+          <t>1353712-9-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2358,27 +2358,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.981.150-K</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION REGIONAL DE ÑUBLE SERPAT</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>285</v>
+        <v>1227.61</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1016-17-CM26</t>
+          <t>1700-19-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>38.12</v>
+        <v>700.38</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1016-18-CM26</t>
+          <t>1059240-10-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>173.09</v>
+        <v>867.22</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1016-19-CM26</t>
+          <t>1700-20-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2541,12 +2541,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2586,13 +2586,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>355.75</v>
+        <v>69.13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1051765-339-CM26</t>
+          <t>1700-21-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2602,27 +2602,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>62.000.570-3</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>983.89</v>
+        <v>122.32</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1043030-14-CM26</t>
+          <t>1208103-10-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2663,12 +2663,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>62.000.480-4</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Secretaria Ministerial de Educación Región Ñuble</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>261.83</v>
+        <v>506.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1049242-29-CM26</t>
+          <t>1208103-12-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>62.000.430-8</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Secretaria Regional Ministerial de las Artes y el</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2769,13 +2769,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>160.52</v>
+        <v>235.66</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1049242-27-CM26</t>
+          <t>1016-15-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2785,27 +2785,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>62.000.430-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Secretaria Regional Ministerial de las Artes y el</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2830,13 +2830,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>188.24</v>
+        <v>100.72</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1049242-28-CM26</t>
+          <t>1016-16-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2846,27 +2846,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>62.000.430-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Secretaria Regional Ministerial de las Artes y el</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>198.94</v>
+        <v>285</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1039043-44-CM26</t>
+          <t>1016-17-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2907,27 +2907,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2952,13 +2952,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>267.92</v>
+        <v>38.12</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4121-38-CM26</t>
+          <t>1016-18-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2968,12 +2968,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2983,12 +2983,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>302.78</v>
+        <v>173.09</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1173803-6-CM26</t>
+          <t>1016-19-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3029,27 +3029,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3074,13 +3074,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>111.74</v>
+        <v>355.75</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1393-279-CM26</t>
+          <t>1051765-339-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3090,27 +3090,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>62.000.570-3</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>Dirección Regional de Ñuble</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>580.45</v>
+        <v>983.89</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1208103-25-CM26</t>
+          <t>1043030-14-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>62.000.480-4</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>Secretaria Ministerial de Educación Región Ñuble</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3196,13 +3196,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>363.69</v>
+        <v>261.83</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1016-30-CM26</t>
+          <t>1039043-44-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3212,27 +3212,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3257,13 +3257,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>148.86</v>
+        <v>267.92</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1016-32-CM26</t>
+          <t>4121-38-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3318,13 +3318,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>116.47</v>
+        <v>302.78</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1016-34-CM26</t>
+          <t>1049242-27-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3334,27 +3334,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.430-8</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Secretaria Regional Ministerial de las Artes y el</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JETSMART</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3379,13 +3379,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>193.39</v>
+        <v>188.24</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1016-35-CM26</t>
+          <t>1049242-28-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3395,27 +3395,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.430-8</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Secretaria Regional Ministerial de las Artes y el</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JETSMART</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>193.92</v>
+        <v>198.94</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3784-298-CM26</t>
+          <t>1049242-29-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3456,12 +3456,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>62.000.430-8</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>Secretaria Regional Ministerial de las Artes y el</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3501,13 +3501,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>275.15</v>
+        <v>160.52</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3841-79-CM26</t>
+          <t>1173803-6-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3522,22 +3522,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.141.600-3</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PEMUCO</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3562,13 +3562,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>108.06</v>
+        <v>111.74</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1016-40-CM26</t>
+          <t>1393-279-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>JETSMART</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3623,18 +3623,18 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>214.94</v>
+        <v>580.45</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1016-47-SE26</t>
+          <t>1208103-25-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2239-23-LP10</t>
+          <t>2239-16-LR23</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3644,22 +3644,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3677,29 +3677,25 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>275.41</v>
+        <v>363.69</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1016-48-SE26</t>
+          <t>1016-32-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2239-23-LP10</t>
+          <t>2239-16-LR23</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3709,7 +3705,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3742,24 +3738,20 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>275.41</v>
+        <v>116.47</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1016-49-CM26</t>
+          <t>1016-34-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3774,7 +3766,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3814,13 +3806,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>355.15</v>
+        <v>193.39</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>4886-73-CM26</t>
+          <t>1016-30-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3830,27 +3822,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3875,13 +3867,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>127.62</v>
+        <v>148.86</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1016-58-CM26</t>
+          <t>1016-35-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3891,12 +3883,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3936,13 +3928,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>416.71</v>
+        <v>193.92</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4886-82-CM26</t>
+          <t>3784-298-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3952,12 +3944,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3967,12 +3959,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>69.150.200-7</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3982,12 +3974,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JETSMART</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3997,13 +3989,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>259.57</v>
+        <v>275.15</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4886-84-CM26</t>
+          <t>3841-79-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4013,27 +4005,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>69.141.600-3</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>I MUNICIPALIDAD DE PEMUCO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4043,12 +4035,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JETSMART</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4058,13 +4050,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>129.79</v>
+        <v>108.06</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4886-80-CM26</t>
+          <t>1016-40-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4074,27 +4066,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4104,12 +4096,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4119,43 +4111,43 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>320.2</v>
+        <v>214.94</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4886-81-CM26</t>
+          <t>1016-47-SE26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2239-16-LR23</t>
+          <t>2239-23-LP10</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4173,35 +4165,39 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>393.01</v>
+        <v>275.41</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3841-114-CM26</t>
+          <t>1016-48-SE26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2239-16-LR23</t>
+          <t>2239-23-LP10</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4211,12 +4207,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.141.600-3</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PEMUCO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4226,28 +4222,32 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>272.58</v>
+        <v>275.41</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1173803-8-CM26</t>
+          <t>1016-49-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4257,27 +4257,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4302,13 +4302,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>157.06</v>
+        <v>355.15</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1059240-24-CM26</t>
+          <t>4886-73-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4323,22 +4323,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>53.312.479-8</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4363,13 +4363,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>536.88</v>
+        <v>127.62</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1059240-26-CM26</t>
+          <t>1016-58-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4424,13 +4424,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>414.57</v>
+        <v>416.71</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1016-63-CM26</t>
+          <t>4886-84-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4445,22 +4445,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>53.312.479-8</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4485,13 +4485,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>155.71</v>
+        <v>129.79</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1016-65-CM26</t>
+          <t>4886-82-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4506,22 +4506,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>53.312.479-8</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4546,13 +4546,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>131.27</v>
+        <v>259.57</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1016-64-CM26</t>
+          <t>4886-81-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4567,22 +4567,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>53.312.479-8</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4607,13 +4607,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>137.98</v>
+        <v>393.01</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1016-62-CM26</t>
+          <t>4886-80-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4628,22 +4628,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>53.312.479-8</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>170.8</v>
+        <v>320.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1016-61-CM26</t>
+          <t>3841-114-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.141.600-3</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE PEMUCO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JETSMART</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4729,13 +4729,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>205.76</v>
+        <v>272.58</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1016-60-CM26</t>
+          <t>1173803-8-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4750,22 +4750,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4790,13 +4790,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>232.92</v>
+        <v>157.06</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1016-67-CM26</t>
+          <t>1059240-24-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4821,12 +4821,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4836,12 +4836,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4851,13 +4851,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>118.9</v>
+        <v>536.88</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1016-68-CM26</t>
+          <t>1059240-26-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4882,12 +4882,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4912,13 +4912,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>109.53</v>
+        <v>414.57</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1016-69-CM26</t>
+          <t>1016-65-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4973,13 +4973,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>283.23</v>
+        <v>131.27</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1016-70-CM26</t>
+          <t>1016-63-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5034,13 +5034,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>367.03</v>
+        <v>155.71</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1016-71-CM26</t>
+          <t>1016-64-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5095,13 +5095,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>269.99</v>
+        <v>137.98</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1059240-29-CM26</t>
+          <t>1016-61-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5156,13 +5156,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>400.42</v>
+        <v>205.76</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2705-1225-CM26</t>
+          <t>1016-60-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5172,27 +5172,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5217,13 +5217,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>58.17</v>
+        <v>232.92</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2705-1227-CM26</t>
+          <t>1016-62-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5233,27 +5233,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5278,13 +5278,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>102.69</v>
+        <v>170.8</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1155683-107-CM26</t>
+          <t>1016-67-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5294,27 +5294,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5339,13 +5339,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>178.78</v>
+        <v>118.9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1049242-52-CM26</t>
+          <t>1016-68-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>62.000.430-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5400,6 +5400,494 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
+        <v>109.53</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1016-69-CM26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>283.23</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1016-70-CM26</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>367.03</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1016-71-CM26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>269.99</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1059240-29-CM26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>400.42</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2705-1225-CM26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>60.911.006-6</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>JetSMART</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>58.17</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2705-1227-CM26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>60.911.006-6</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>JetSMART</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>102.69</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1155683-107-CM26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>178.78</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1049242-52-CM26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>62.000.430-8</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
         <v>806.36</v>
       </c>
     </row>

--- a/docs/oc-regiones/pasajes-aereos-nacionales/nuble.xlsx
+++ b/docs/oc-regiones/pasajes-aereos-nacionales/nuble.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ñuble" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ñuble" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:M168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1173803-8-CM25</t>
+          <t>1393-1-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>177.68</v>
+        <v>315.49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1059240-23-CM25</t>
+          <t>1393-3-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>219.38</v>
+        <v>175.14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1208103-34-CM25</t>
+          <t>1059109-44-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>467.8</v>
+        <v>1498.57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1063487-17-CM25</t>
+          <t>1036569-67-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.390-5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>106.51</v>
+        <v>469.77</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1016-78-CM25</t>
+          <t>1036569-68-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.390-5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>118.6</v>
+        <v>30.26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1049242-92-CM25</t>
+          <t>1036569-69-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>62.000.430-8</t>
+          <t>62.000.390-5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>449.8</v>
+        <v>30.26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1043030-81-CM25</t>
+          <t>1208103-9-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>62.000.480-4</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>423.01</v>
+        <v>57.01</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2705-1573-CM25</t>
+          <t>1051425-25-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>454.7</v>
+        <v>517.83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1700-106-CM25</t>
+          <t>1051425-26-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>95.84</v>
+        <v>450.44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1700-107-CM25</t>
+          <t>1059240-10-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>71.47</v>
+        <v>146.61</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2705-1649-CM25</t>
+          <t>1700-19-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>492.68</v>
+        <v>164.61</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1016-111-CM25</t>
+          <t>1051765-342-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.570-3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>285.94</v>
+        <v>258.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1059240-73-CM25</t>
+          <t>1700-28-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>316.29</v>
+        <v>204.73</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1016-114-CM25</t>
+          <t>1700-29-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>407.34</v>
+        <v>204.73</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2705-1746-CM25</t>
+          <t>2705-539-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>614.0599999999999</v>
+        <v>391.08</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1059240-78-CM25</t>
+          <t>2705-540-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>390.72</v>
+        <v>163.06</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1173803-28-CM25</t>
+          <t>2705-556-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>155.35</v>
+        <v>204.65</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1063487-22-CM25</t>
+          <t>1173803-8-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>452.8</v>
+        <v>177.68</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4886-225-CM25</t>
+          <t>2705-644-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,27 +1622,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,43 +1667,43 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>116.76</v>
+        <v>280.29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1059240-85-SE25</t>
+          <t>1039043-51-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2239-23-LP10</t>
+          <t>2239-16-LR23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1721,24 +1721,20 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>99.11</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1016-125-CM25</t>
+          <t>1059240-23-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1748,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1763,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1778,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1793,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>367.43</v>
+        <v>219.38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1059240-1-CM26</t>
+          <t>1208103-16-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1809,27 +1805,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1854,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>145.33</v>
+        <v>390.27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1057509-954-CM26</t>
+          <t>1208103-21-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1870,27 +1866,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.607.001-0</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO HERMINDA MARTIN</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1900,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1915,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>358.29</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1051765-41-CM26</t>
+          <t>1049242-34-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1931,27 +1927,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>62.000.570-3</t>
+          <t>62.000.430-8</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1976,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>420.99</v>
+        <v>1437.25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1057509-1306-CM26</t>
+          <t>1059240-32-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1992,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2007,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.607.001-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO HERMINDA MARTIN</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2037,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>741.37</v>
+        <v>66.42</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1051765-107-CM26</t>
+          <t>1059240-34-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2053,27 +2049,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>62.000.570-3</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2083,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2098,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>160.98</v>
+        <v>172.15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1063487-7-CM26</t>
+          <t>1036569-143-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2114,27 +2110,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.390-5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2159,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>84.40000000000001</v>
+        <v>447.01</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1051765-111-CM26</t>
+          <t>1036569-146-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2175,27 +2171,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>62.000.570-3</t>
+          <t>62.000.390-5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2220,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>313.95</v>
+        <v>444.82</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1059240-6-CM26</t>
+          <t>1700-59-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2236,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2251,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2266,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2281,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>84.08</v>
+        <v>191.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1059240-8-CM26</t>
+          <t>1700-58-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2297,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2312,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2327,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2342,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>90.52</v>
+        <v>189.07</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1353712-9-CM26</t>
+          <t>2705-922-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2358,27 +2354,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.981.150-K</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE ÑUBLE SERPAT</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2403,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1227.61</v>
+        <v>165.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1700-19-CM26</t>
+          <t>1208103-34-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2419,27 +2415,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2464,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>700.38</v>
+        <v>467.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1059240-10-CM26</t>
+          <t>1059240-37-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2480,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2510,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2525,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>867.22</v>
+        <v>181.05</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1700-20-CM26</t>
+          <t>1208103-33-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2541,27 +2537,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2586,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>69.13</v>
+        <v>229.42</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1700-21-CM26</t>
+          <t>2705-971-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2602,12 +2598,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2617,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2632,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2647,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>122.32</v>
+        <v>143.16</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1208103-10-CM26</t>
+          <t>1700-63-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2663,27 +2659,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2708,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>506.2</v>
+        <v>172.89</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1208103-12-CM26</t>
+          <t>1051765-794-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2724,12 +2720,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2739,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>62.000.570-3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2754,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2769,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>235.66</v>
+        <v>135.31</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1016-15-CM26</t>
+          <t>3673-389-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2785,12 +2781,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2800,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2815,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2830,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>100.72</v>
+        <v>1469.02</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1016-16-CM26</t>
+          <t>1060500-37-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2846,27 +2842,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.510-k</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2876,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2891,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>285</v>
+        <v>84.61</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1016-17-CM26</t>
+          <t>1059109-165-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2907,27 +2903,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2937,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2952,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>38.12</v>
+        <v>171.28</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1016-18-CM26</t>
+          <t>3673-388-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2968,12 +2964,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2983,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2998,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3013,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>173.09</v>
+        <v>1611.74</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1016-19-CM26</t>
+          <t>1063487-17-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3029,12 +3025,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3074,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>355.75</v>
+        <v>106.51</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1051765-339-CM26</t>
+          <t>2705-1145-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3090,27 +3086,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>62.000.570-3</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3135,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>983.89</v>
+        <v>141.49</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1043030-14-CM26</t>
+          <t>1059240-47-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3151,27 +3147,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>62.000.480-4</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Secretaria Ministerial de Educación Región Ñuble</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3181,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3196,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>261.83</v>
+        <v>176.67</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1039043-44-CM26</t>
+          <t>1059240-46-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3212,27 +3208,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3257,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>267.92</v>
+        <v>118.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4121-38-CM26</t>
+          <t>1016-78-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3273,12 +3269,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3288,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3318,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>302.78</v>
+        <v>118.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1049242-27-CM26</t>
+          <t>1059240-50-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3334,27 +3330,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>62.000.430-8</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Secretaria Regional Ministerial de las Artes y el</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3364,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3379,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>188.24</v>
+        <v>68.02</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1049242-28-CM26</t>
+          <t>1059240-51-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3395,27 +3391,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>62.000.430-8</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Secretaria Regional Ministerial de las Artes y el</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3425,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3440,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>198.94</v>
+        <v>597.27</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1049242-29-CM26</t>
+          <t>1059240-52-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3456,27 +3452,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>62.000.430-8</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Secretaria Regional Ministerial de las Artes y el</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3486,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3501,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>160.52</v>
+        <v>125.75</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1173803-6-CM26</t>
+          <t>1059240-53-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3517,27 +3513,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3562,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>111.74</v>
+        <v>216.85</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1393-279-CM26</t>
+          <t>1208103-42-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3578,27 +3574,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3608,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3623,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>580.45</v>
+        <v>59.56</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1208103-25-CM26</t>
+          <t>1208103-43-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3639,12 +3635,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3684,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>363.69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1016-32-CM26</t>
+          <t>1059240-55-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3700,12 +3696,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3715,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3745,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>116.47</v>
+        <v>1163.59</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1016-34-CM26</t>
+          <t>1700-85-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3761,12 +3757,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3776,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3806,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>193.39</v>
+        <v>115.61</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1016-30-CM26</t>
+          <t>1049242-69-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3822,27 +3818,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.430-8</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3852,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3867,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>148.86</v>
+        <v>173.05</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1016-35-CM26</t>
+          <t>1059109-184-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3883,27 +3879,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3928,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>193.92</v>
+        <v>210.58</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3784-298-CM26</t>
+          <t>1700-91-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3944,27 +3940,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3974,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3989,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>275.15</v>
+        <v>146.45</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3841-79-CM26</t>
+          <t>1039043-86-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4005,27 +4001,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.141.600-3</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PEMUCO</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4035,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4050,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>108.06</v>
+        <v>35.63</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1016-40-CM26</t>
+          <t>3673-495-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4066,12 +4062,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4081,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4096,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4111,43 +4107,43 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>214.94</v>
+        <v>697.78</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1016-47-SE26</t>
+          <t>1113015-240-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2239-23-LP10</t>
+          <t>2239-16-LR23</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4165,54 +4161,50 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>275.41</v>
+        <v>300.24</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1016-48-SE26</t>
+          <t>1049242-91-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2239-23-LP10</t>
+          <t>2239-16-LR23</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.430-8</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4230,24 +4222,20 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>275.41</v>
+        <v>1218.89</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1016-49-CM26</t>
+          <t>1049242-90-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4257,27 +4245,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.430-8</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4287,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4302,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>355.15</v>
+        <v>210.75</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4886-73-CM26</t>
+          <t>1049242-92-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4318,12 +4306,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4333,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>62.000.430-8</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4348,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4363,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>127.62</v>
+        <v>449.8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1016-58-CM26</t>
+          <t>1059240-63-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4379,12 +4367,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4394,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4424,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>416.71</v>
+        <v>279.1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4886-84-CM26</t>
+          <t>1059240-64-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4440,27 +4428,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4485,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>129.79</v>
+        <v>100.22</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4886-82-CM26</t>
+          <t>1043030-82-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4501,12 +4489,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4516,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>62.000.480-4</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4531,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4546,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>259.57</v>
+        <v>529.86</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4886-81-CM26</t>
+          <t>1043030-81-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4562,12 +4550,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4577,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>62.000.480-4</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4592,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4607,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>393.01</v>
+        <v>423.01</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4886-80-CM26</t>
+          <t>1700-95-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4623,27 +4611,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4653,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4668,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>320.2</v>
+        <v>108.02</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3841-114-CM26</t>
+          <t>1700-96-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4684,12 +4672,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4699,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.141.600-3</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PEMUCO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4714,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4729,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>272.58</v>
+        <v>57.38</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1173803-8-CM26</t>
+          <t>1059109-200-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4745,12 +4733,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4760,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4790,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>157.06</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1059240-24-CM26</t>
+          <t>1059240-67-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4806,12 +4794,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4851,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>536.88</v>
+        <v>230.39</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1059240-26-CM26</t>
+          <t>1059240-70-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4867,12 +4855,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4897,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4912,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>414.57</v>
+        <v>317.97</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1016-65-CM26</t>
+          <t>1208103-52-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4928,27 +4916,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4973,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>131.27</v>
+        <v>436.05</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1016-63-CM26</t>
+          <t>1208103-53-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4989,27 +4977,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5034,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>155.71</v>
+        <v>647.37</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1016-64-CM26</t>
+          <t>2705-1570-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5050,12 +5038,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5065,12 +5053,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5080,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5095,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>137.98</v>
+        <v>380.82</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1016-61-CM26</t>
+          <t>2705-1573-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5111,12 +5099,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5126,12 +5114,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5156,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>205.76</v>
+        <v>454.7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1016-60-CM26</t>
+          <t>1700-106-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5172,12 +5160,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5187,12 +5175,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5217,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>232.92</v>
+        <v>95.84</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1016-62-CM26</t>
+          <t>1700-107-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5233,12 +5221,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5248,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5263,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JETSMART</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5278,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>170.8</v>
+        <v>71.47</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1016-67-CM26</t>
+          <t>2705-1649-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5294,12 +5282,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5309,12 +5297,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5324,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5339,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>118.9</v>
+        <v>492.68</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1016-68-CM26</t>
+          <t>1016-111-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5355,12 +5343,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5400,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>109.53</v>
+        <v>285.94</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1016-69-CM26</t>
+          <t>1059240-73-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5416,12 +5404,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5431,12 +5419,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5461,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>283.23</v>
+        <v>316.29</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1016-70-CM26</t>
+          <t>1016-114-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5477,12 +5465,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5522,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>367.03</v>
+        <v>407.34</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1016-71-CM26</t>
+          <t>2705-1746-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5538,12 +5526,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5553,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5583,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>269.99</v>
+        <v>614.0599999999999</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1059240-29-CM26</t>
+          <t>4886-225-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5599,27 +5587,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>53.312.479-8</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5629,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5644,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>400.42</v>
+        <v>116.76</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2705-1225-CM26</t>
+          <t>1059240-78-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5660,27 +5648,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5690,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5705,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>58.17</v>
+        <v>390.72</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2705-1227-CM26</t>
+          <t>1173803-28-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5721,27 +5709,27 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5751,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5766,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>102.69</v>
+        <v>155.35</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1155683-107-CM26</t>
+          <t>1063487-22-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5782,27 +5770,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5827,68 +5815,4899 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>178.78</v>
+        <v>452.8</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>1059240-85-SE25</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-23-LP10</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>99.11</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1016-125-CM25</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>367.43</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1059240-1-CM26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>145.33</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1057509-954-CM26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>61.607.001-0</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO HERMINDA MARTIN</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>JETSMART</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>358.29</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1051765-41-CM26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>62.000.570-3</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Dirección Regional de Ñuble</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>420.99</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1057509-1306-CM26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>61.607.001-0</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO HERMINDA MARTIN</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>741.37</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1051765-107-CM26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>62.000.570-3</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Dirección Regional de Ñuble</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>160.98</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1063487-7-CM26</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>84.40000000000001</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1051765-111-CM26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>62.000.570-3</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Dirección Regional de Ñuble</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>313.95</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1059240-6-CM26</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>84.08</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1059240-8-CM26</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>JETSMART</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>90.52</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1353712-9-CM26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>61.981.150-K</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>DIRECCION REGIONAL DE ÑUBLE SERPAT</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>1227.61</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>1059240-10-CM26</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>867.22</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1700-19-CM26</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>700.38</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>1700-20-CM26</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>69.13</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>1700-21-CM26</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>122.32</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>1208103-10-CM26</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>506.2</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>1208103-12-CM26</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>235.66</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>1016-15-CM26</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>100.72</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1016-17-CM26</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>38.12</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>1016-16-CM26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>1016-18-CM26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>173.09</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>1016-19-CM26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>355.75</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>1051765-339-CM26</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>62.000.570-3</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Dirección Regional de Ñuble</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>983.89</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1043030-14-CM26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>62.000.480-4</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Secretaria Ministerial de Educación Región Ñuble</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>261.83</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>1039043-44-CM26</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>61.307.000-1</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>267.92</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>4121-38-CM26</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>69.140.300-9</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>302.78</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1049242-27-CM26</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>62.000.430-8</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Secretaria Regional Ministerial de las Artes y el</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>JETSMART</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>188.24</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1049242-28-CM26</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>62.000.430-8</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Secretaria Regional Ministerial de las Artes y el</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>JETSMART</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>198.94</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1049242-29-CM26</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>62.000.430-8</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Secretaria Regional Ministerial de las Artes y el</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>160.52</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>1173803-6-CM26</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>70.816.700-2</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>111.74</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>1393-279-CM26</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>69.140.300-9</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>JETSMART</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>580.45</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>1208103-25-CM26</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>363.69</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1016-30-CM26</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>148.86</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1016-32-CM26</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>116.47</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1016-34-CM26</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>193.39</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>1016-35-CM26</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>193.92</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>3784-298-CM26</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>69.150.200-7</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>JETSMART</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>275.15</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>3841-79-CM26</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>69.141.600-3</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PEMUCO</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>JETSMART</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>108.06</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>1016-40-CM26</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>214.94</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>1016-47-SE26</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2239-23-LP10</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>275.41</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>1016-48-SE26</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2239-23-LP10</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>275.41</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>1016-49-CM26</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>355.15</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>4886-73-CM26</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>53.312.479-8</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>127.62</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>4886-80-CM26</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>53.312.479-8</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>320.2</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>4886-81-CM26</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>53.312.479-8</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="n">
+        <v>393.01</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>4886-82-CM26</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>53.312.479-8</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="n">
+        <v>259.57</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>4886-84-CM26</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>53.312.479-8</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>129.79</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>1016-58-CM26</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>416.71</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>3841-114-CM26</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>69.141.600-3</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PEMUCO</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>JETSMART</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>272.58</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>1173803-8-CM26</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>70.816.700-2</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="n">
+        <v>157.06</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>1059240-24-CM26</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="n">
+        <v>536.88</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>1059240-26-CM26</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>414.57</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>1016-60-CM26</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>232.92</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>1016-61-CM26</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="n">
+        <v>205.76</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>1016-62-CM26</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="n">
+        <v>170.8</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>1016-63-CM26</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="n">
+        <v>155.71</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>1016-64-CM26</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="n">
+        <v>137.98</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>1016-65-CM26</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="n">
+        <v>131.27</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>1016-67-CM26</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>118.9</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>1016-68-CM26</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="n">
+        <v>109.53</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>1016-69-CM26</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>283.23</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>1016-70-CM26</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="n">
+        <v>367.03</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>1016-71-CM26</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="n">
+        <v>269.99</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>1059240-29-CM26</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="n">
+        <v>400.42</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2705-1227-CM26</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>60.911.006-6</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>JetSMART</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="n">
+        <v>102.69</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2705-1225-CM26</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>60.911.006-6</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>JetSMART</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="n">
+        <v>58.17</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>1059240-34-CM26</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="n">
+        <v>793.52</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>1059240-35-CM26</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="n">
+        <v>439.95</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>1057509-9023-CM26</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>61.607.001-0</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO HERMINDA MARTIN</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="n">
+        <v>809.48</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>1173805-20-CM26</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>70.816.700-2</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="n">
+        <v>210.31</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>1173805-21-CM26</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>70.816.700-2</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="n">
+        <v>300.92</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>1059240-39-CM26</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="n">
+        <v>1207.12</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>1155683-107-CM26</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="n">
+        <v>178.78</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>1049242-50-CM26</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>62.000.430-8</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="n">
+        <v>194.98</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>1700-86-CM26</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="n">
+        <v>157.65</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
           <t>1049242-52-CM26</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
         <is>
           <t>ago-2026</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D165" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E165" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F165" t="inlineStr">
         <is>
           <t>62.000.430-8</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G165" t="inlineStr">
         <is>
           <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="n">
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="n">
         <v>806.36</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>1049242-53-CM26</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>62.000.430-8</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="n">
+        <v>1209.54</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>1059240-42-CM26</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="n">
+        <v>790.05</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>1059240-44-CM26</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="n">
+        <v>435.34</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/pasajes-aereos-nacionales/nuble.xlsx
+++ b/docs/oc-regiones/pasajes-aereos-nacionales/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M168"/>
+  <dimension ref="A1:M150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1673,7 +1673,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1039043-51-CM25</t>
+          <t>1208103-16-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>35.48</v>
+        <v>390.27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1059240-23-CM25</t>
+          <t>1039043-51-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1754,17 +1754,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>219.38</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1208103-16-CM25</t>
+          <t>1059240-23-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1815,17 +1815,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>390.27</v>
+        <v>219.38</v>
       </c>
     </row>
     <row r="24">
@@ -2405,7 +2405,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1208103-34-CM25</t>
+          <t>1208103-33-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>467.8</v>
+        <v>229.42</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1059240-37-CM25</t>
+          <t>1208103-34-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>181.05</v>
+        <v>467.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1208103-33-CM25</t>
+          <t>1059240-37-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2547,17 +2547,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>229.42</v>
+        <v>181.05</v>
       </c>
     </row>
     <row r="36">
@@ -2771,7 +2771,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3673-389-CM25</t>
+          <t>1060500-37-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2791,17 +2791,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>62.000.510-k</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1469.02</v>
+        <v>84.61</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1060500-37-CM25</t>
+          <t>1059109-165-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>62.000.510-k</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>84.61</v>
+        <v>171.28</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1059109-165-CM25</t>
+          <t>3673-388-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2913,17 +2913,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>171.28</v>
+        <v>1611.74</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3673-388-CM25</t>
+          <t>3673-389-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1611.74</v>
+        <v>1469.02</v>
       </c>
     </row>
     <row r="43">
@@ -3137,7 +3137,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1059240-47-CM25</t>
+          <t>1059240-46-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>176.67</v>
+        <v>118.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1059240-46-CM25</t>
+          <t>1059240-47-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>118.8</v>
+        <v>176.67</v>
       </c>
     </row>
     <row r="47">
@@ -3320,7 +3320,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1059240-50-CM25</t>
+          <t>1059240-51-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>68.02</v>
+        <v>597.27</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1059240-51-CM25</t>
+          <t>1059240-52-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>597.27</v>
+        <v>125.75</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1059240-52-CM25</t>
+          <t>1059240-53-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>125.75</v>
+        <v>216.85</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1059240-53-CM25</t>
+          <t>1059240-50-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>216.85</v>
+        <v>68.02</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1208103-42-CM25</t>
+          <t>1208103-43-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>59.56</v>
+        <v>76</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1208103-43-CM25</t>
+          <t>1208103-42-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>76</v>
+        <v>59.56</v>
       </c>
     </row>
     <row r="54">
@@ -4235,7 +4235,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1049242-90-CM25</t>
+          <t>1049242-92-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>210.75</v>
+        <v>449.8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1049242-92-CM25</t>
+          <t>1049242-90-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>449.8</v>
+        <v>210.75</v>
       </c>
     </row>
     <row r="65">
@@ -4479,7 +4479,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1043030-82-CM25</t>
+          <t>1043030-81-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>529.86</v>
+        <v>423.01</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1043030-81-CM25</t>
+          <t>1043030-82-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>423.01</v>
+        <v>529.86</v>
       </c>
     </row>
     <row r="69">
@@ -4845,7 +4845,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1059240-70-CM25</t>
+          <t>1208103-53-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4865,17 +4865,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>317.97</v>
+        <v>647.37</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1208103-52-CM25</t>
+          <t>1059240-70-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4926,17 +4926,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>436.05</v>
+        <v>317.97</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1208103-53-CM25</t>
+          <t>1208103-52-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>647.37</v>
+        <v>436.05</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2705-1570-CM25</t>
+          <t>2705-1573-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>380.82</v>
+        <v>454.7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2705-1573-CM25</t>
+          <t>2705-1570-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>454.7</v>
+        <v>380.82</v>
       </c>
     </row>
     <row r="78">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5333,7 +5333,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1016-111-CM25</t>
+          <t>1059240-73-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>285.94</v>
+        <v>316.29</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1059240-73-CM25</t>
+          <t>2705-1746-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>316.29</v>
+        <v>614.0599999999999</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1016-114-CM25</t>
+          <t>1059240-78-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>407.34</v>
+        <v>390.72</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2705-1746-CM25</t>
+          <t>1063487-22-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>614.0599999999999</v>
+        <v>452.8</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4886-225-CM25</t>
+          <t>1173805-26-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5592,22 +5592,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5632,18 +5632,18 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>116.76</v>
+        <v>184.88</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1059240-78-CM25</t>
+          <t>1059240-85-SE25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2239-16-LR23</t>
+          <t>2239-23-LP10</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5678,28 +5678,32 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>390.72</v>
+        <v>99.11</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1173803-28-CM25</t>
+          <t>1059240-1-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5709,12 +5713,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,12 +5728,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5754,13 +5758,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>155.35</v>
+        <v>145.33</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1063487-22-CM25</t>
+          <t>1173805-1-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5770,27 +5774,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5815,28 +5819,28 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>452.8</v>
+        <v>643.17</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1059240-85-SE25</t>
+          <t>1057509-954-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2239-23-LP10</t>
+          <t>2239-16-LR23</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5846,12 +5850,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.607.001-0</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>HOSPITAL CLINICO HERMINDA MARTIN</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,32 +5865,28 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>99.11</v>
+        <v>358.29</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1016-125-CM25</t>
+          <t>1051765-41-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5896,27 +5896,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.570-3</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5941,13 +5941,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>367.43</v>
+        <v>420.99</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1059240-1-CM26</t>
+          <t>1057509-1306-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.607.001-0</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>HOSPITAL CLINICO HERMINDA MARTIN</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6002,13 +6002,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>145.33</v>
+        <v>741.37</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1057509-954-CM26</t>
+          <t>1051765-107-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6018,27 +6018,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.607.001-0</t>
+          <t>62.000.570-3</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO HERMINDA MARTIN</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6063,13 +6063,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>358.29</v>
+        <v>160.98</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1051765-41-CM26</t>
+          <t>1063487-7-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6079,27 +6079,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>62.000.570-3</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6124,13 +6124,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>420.99</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1057509-1306-CM26</t>
+          <t>1051765-111-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6140,27 +6140,27 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.607.001-0</t>
+          <t>62.000.570-3</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO HERMINDA MARTIN</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>741.37</v>
+        <v>313.95</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1051765-107-CM26</t>
+          <t>1059240-6-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6201,27 +6201,27 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>62.000.570-3</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6246,13 +6246,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>160.98</v>
+        <v>84.08</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1063487-7-CM26</t>
+          <t>1059240-8-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6307,13 +6307,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>84.40000000000001</v>
+        <v>90.52</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1051765-111-CM26</t>
+          <t>1353712-9-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6323,12 +6323,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>62.000.570-3</t>
+          <t>61.981.150-K</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6368,13 +6368,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>313.95</v>
+        <v>1227.61</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1059240-6-CM26</t>
+          <t>1059240-10-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6414,12 +6414,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6429,13 +6429,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>84.08</v>
+        <v>867.22</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1059240-8-CM26</t>
+          <t>1700-19-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>90.52</v>
+        <v>700.38</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1353712-9-CM26</t>
+          <t>1700-21-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6511,22 +6511,22 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.981.150-K</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE ÑUBLE SERPAT</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6551,13 +6551,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1227.61</v>
+        <v>122.32</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1059240-10-CM26</t>
+          <t>1700-20-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6612,13 +6612,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>867.22</v>
+        <v>69.13</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1700-19-CM26</t>
+          <t>1208103-10-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6628,27 +6628,27 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6673,13 +6673,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>700.38</v>
+        <v>506.2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1700-20-CM26</t>
+          <t>1208103-12-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6689,27 +6689,27 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6734,13 +6734,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>69.13</v>
+        <v>235.66</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1700-21-CM26</t>
+          <t>1051765-339-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6750,27 +6750,27 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>62.000.570-3</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6780,12 +6780,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6795,13 +6795,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>122.32</v>
+        <v>983.89</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1208103-10-CM26</t>
+          <t>1043030-14-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6826,12 +6826,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>62.000.480-4</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6856,13 +6856,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>506.2</v>
+        <v>261.83</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1208103-12-CM26</t>
+          <t>1039043-44-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6917,13 +6917,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>235.66</v>
+        <v>267.92</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1016-15-CM26</t>
+          <t>4121-38-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6978,13 +6978,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>100.72</v>
+        <v>302.78</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1016-17-CM26</t>
+          <t>1049242-27-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6994,27 +6994,27 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.430-8</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7039,13 +7039,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>38.12</v>
+        <v>188.24</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1016-16-CM26</t>
+          <t>1049242-28-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7055,27 +7055,27 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.430-8</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7100,13 +7100,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>285</v>
+        <v>198.94</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1016-18-CM26</t>
+          <t>1049242-29-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7116,27 +7116,27 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.430-8</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7161,13 +7161,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>173.09</v>
+        <v>160.52</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1016-19-CM26</t>
+          <t>1347775-9-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7177,27 +7177,27 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7222,13 +7222,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>355.75</v>
+        <v>363.69</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1051765-339-CM26</t>
+          <t>1208103-25-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>62.000.570-3</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7283,13 +7283,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>983.89</v>
+        <v>363.69</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1043030-14-CM26</t>
+          <t>1393-279-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7299,27 +7299,27 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>62.000.480-4</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Secretaria Ministerial de Educación Región Ñuble</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7329,12 +7329,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7344,13 +7344,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>261.83</v>
+        <v>580.45</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1039043-44-CM26</t>
+          <t>1016-35-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7360,27 +7360,27 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7405,13 +7405,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>267.92</v>
+        <v>193.92</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>4121-38-CM26</t>
+          <t>3784-298-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7421,27 +7421,27 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>69.150.200-7</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7451,12 +7451,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7466,13 +7466,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>302.78</v>
+        <v>275.15</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1049242-27-CM26</t>
+          <t>3841-79-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7482,27 +7482,27 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>62.000.430-8</t>
+          <t>69.141.600-3</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Secretaria Regional Ministerial de las Artes y el</t>
+          <t>I MUNICIPALIDAD DE PEMUCO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7527,13 +7527,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>188.24</v>
+        <v>108.06</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1049242-28-CM26</t>
+          <t>1173805-10-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7543,12 +7543,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>62.000.430-8</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Secretaria Regional Ministerial de las Artes y el</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7588,13 +7588,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>198.94</v>
+        <v>382.82</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1049242-29-CM26</t>
+          <t>4886-84-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>62.000.430-8</t>
+          <t>53.312.479-8</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Secretaria Regional Ministerial de las Artes y el</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7649,13 +7649,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>160.52</v>
+        <v>129.79</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1173803-6-CM26</t>
+          <t>3841-114-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7665,27 +7665,27 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>69.141.600-3</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE PEMUCO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7710,13 +7710,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>111.74</v>
+        <v>272.58</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1393-279-CM26</t>
+          <t>1059240-24-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7726,12 +7726,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7771,13 +7771,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>580.45</v>
+        <v>536.88</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1208103-25-CM26</t>
+          <t>1059240-26-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7787,27 +7787,27 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7832,13 +7832,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>363.69</v>
+        <v>414.57</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1016-30-CM26</t>
+          <t>1059240-29-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>148.86</v>
+        <v>400.42</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1016-32-CM26</t>
+          <t>2705-1225-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7909,27 +7909,27 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7939,12 +7939,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7954,13 +7954,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>116.47</v>
+        <v>58.17</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1016-34-CM26</t>
+          <t>2705-1227-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7970,27 +7970,27 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8000,12 +8000,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8015,13 +8015,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>193.39</v>
+        <v>102.69</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1016-35-CM26</t>
+          <t>1059240-34-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8076,13 +8076,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>193.92</v>
+        <v>793.52</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>3784-298-CM26</t>
+          <t>1059240-35-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8092,27 +8092,27 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8122,12 +8122,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8137,13 +8137,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>275.15</v>
+        <v>439.95</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3841-79-CM26</t>
+          <t>1057509-9023-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8153,27 +8153,27 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>69.141.600-3</t>
+          <t>61.607.001-0</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PEMUCO</t>
+          <t>HOSPITAL CLINICO HERMINDA MARTIN</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8183,12 +8183,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>108.06</v>
+        <v>809.48</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1016-40-CM26</t>
+          <t>1173805-20-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8214,27 +8214,27 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8259,43 +8259,43 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>214.94</v>
+        <v>210.31</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1016-47-SE26</t>
+          <t>1173805-21-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2239-23-LP10</t>
+          <t>2239-16-LR23</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8305,47 +8305,43 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>275.41</v>
+        <v>300.92</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1016-48-SE26</t>
+          <t>1059240-39-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2239-23-LP10</t>
+          <t>2239-16-LR23</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8355,12 +8351,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8378,24 +8374,20 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>275.41</v>
+        <v>1207.12</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1016-49-CM26</t>
+          <t>1155683-107-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8405,27 +8397,27 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8450,13 +8442,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>355.15</v>
+        <v>178.78</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>4886-73-CM26</t>
+          <t>1049242-50-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8466,27 +8458,27 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>62.000.430-8</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8511,13 +8503,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>127.62</v>
+        <v>194.98</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>4886-80-CM26</t>
+          <t>1700-86-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8527,27 +8519,27 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8557,12 +8549,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8572,13 +8564,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>320.2</v>
+        <v>157.65</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>4886-81-CM26</t>
+          <t>1049242-53-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8588,27 +8580,27 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>62.000.430-8</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8633,13 +8625,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>393.01</v>
+        <v>1209.54</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>4886-82-CM26</t>
+          <t>1059240-42-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8649,27 +8641,27 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8694,13 +8686,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>259.57</v>
+        <v>790.05</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>4886-84-CM26</t>
+          <t>1049242-52-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8710,27 +8702,27 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>62.000.430-8</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8755,13 +8747,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>129.79</v>
+        <v>806.36</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1016-58-CM26</t>
+          <t>1059240-44-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8771,12 +8763,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8786,12 +8778,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8816,13 +8808,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>416.71</v>
+        <v>435.34</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>3841-114-CM26</t>
+          <t>1059240-47-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8832,12 +8824,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8847,12 +8839,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>69.141.600-3</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PEMUCO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8862,12 +8854,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>JETSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8877,13 +8869,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>272.58</v>
+        <v>65.59</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1173803-8-CM26</t>
+          <t>1059240-48-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8893,27 +8885,27 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8938,13 +8930,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>157.06</v>
+        <v>140.28</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1059240-24-CM26</t>
+          <t>1059240-50-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8954,12 +8946,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8999,13 +8991,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>536.88</v>
+        <v>258.04</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1059240-26-CM26</t>
+          <t>1700-89-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9015,12 +9007,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9030,12 +9022,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9060,13 +9052,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>414.57</v>
+        <v>183.03</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1016-60-CM26</t>
+          <t>1700-90-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9076,12 +9068,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9091,12 +9083,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9106,12 +9098,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -9121,13 +9113,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>232.92</v>
+        <v>94.56999999999999</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1016-61-CM26</t>
+          <t>1059240-52-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9137,12 +9129,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9152,12 +9144,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9182,13 +9174,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>205.76</v>
+        <v>235.56</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1016-62-CM26</t>
+          <t>1059240-53-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9198,12 +9190,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9213,12 +9205,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9243,13 +9235,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>170.8</v>
+        <v>161.39</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1016-63-CM26</t>
+          <t>1700-91-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9259,12 +9251,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9274,12 +9266,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9304,13 +9296,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>155.71</v>
+        <v>175.77</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1016-64-CM26</t>
+          <t>2705-1538-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9320,27 +9312,27 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9365,13 +9357,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>137.98</v>
+        <v>376.42</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1016-65-CM26</t>
+          <t>1059109-95-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9381,12 +9373,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9396,12 +9388,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9426,13 +9418,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>131.27</v>
+        <v>229.76</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1016-67-CM26</t>
+          <t>2705-1543-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9442,27 +9434,27 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9472,12 +9464,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9487,13 +9479,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>118.9</v>
+        <v>113.98</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1016-68-CM26</t>
+          <t>2705-1540-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9503,27 +9495,27 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9533,12 +9525,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9548,13 +9540,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>109.53</v>
+        <v>111.32</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1016-69-CM26</t>
+          <t>1059240-59-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9564,12 +9556,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9579,12 +9571,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9609,1105 +9601,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>283.23</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>1016-70-CM26</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>61.202.000-0</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M151" s="2" t="n">
-        <v>367.03</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>1016-71-CM26</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>61.202.000-0</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M152" s="2" t="n">
-        <v>269.99</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>1059240-29-CM26</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>61.935.400-1</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>MINISTERIO PUBLICO</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M153" s="2" t="n">
-        <v>400.42</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>2705-1227-CM26</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>60.911.006-6</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>JetSMART</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>76.574.879-8</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M154" s="2" t="n">
-        <v>102.69</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>2705-1225-CM26</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>60.911.006-6</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>JetSMART</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>76.574.879-8</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M155" s="2" t="n">
-        <v>58.17</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>1059240-34-CM26</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>61.935.400-1</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>MINISTERIO PUBLICO</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M156" s="2" t="n">
-        <v>793.52</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>1059240-35-CM26</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>61.935.400-1</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>MINISTERIO PUBLICO</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M157" s="2" t="n">
-        <v>439.95</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>1057509-9023-CM26</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>61.607.001-0</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>HOSPITAL CLINICO HERMINDA MARTIN</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>SKY AIRLINE S A</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>88.417.000-1</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M158" s="2" t="n">
-        <v>809.48</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>1173805-20-CM26</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>70.816.700-2</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M159" s="2" t="n">
-        <v>210.31</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>1173805-21-CM26</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>70.816.700-2</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>SKY AIRLINE S A</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>88.417.000-1</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M160" s="2" t="n">
-        <v>300.92</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>1059240-39-CM26</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>61.935.400-1</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>MINISTERIO PUBLICO</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M161" s="2" t="n">
-        <v>1207.12</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>1155683-107-CM26</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>61.313.000-4</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>CORP NACIONAL FORESTAL</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M162" s="2" t="n">
-        <v>178.78</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>1049242-50-CM26</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>62.000.430-8</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M163" s="2" t="n">
-        <v>194.98</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>1700-86-CM26</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>60.301.001-9</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>SKY AIRLINE S A</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>88.417.000-1</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M164" s="2" t="n">
-        <v>157.65</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>1049242-52-CM26</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>62.000.430-8</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M165" s="2" t="n">
-        <v>806.36</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>1049242-53-CM26</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>62.000.430-8</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M166" s="2" t="n">
-        <v>1209.54</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>1059240-42-CM26</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>61.935.400-1</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>MINISTERIO PUBLICO</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M167" s="2" t="n">
-        <v>790.05</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>1059240-44-CM26</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>61.935.400-1</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>MINISTERIO PUBLICO</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M168" s="2" t="n">
-        <v>435.34</v>
+        <v>278.8</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/pasajes-aereos-nacionales/nuble.xlsx
+++ b/docs/oc-regiones/pasajes-aereos-nacionales/nuble.xlsx
@@ -562,7 +562,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5751,7 +6087,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5812,7 +6152,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5873,7 +6217,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5934,7 +6282,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5995,7 +6347,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6056,7 +6412,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6117,7 +6477,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6178,7 +6542,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6239,7 +6607,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6300,7 +6672,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6361,7 +6737,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6422,7 +6802,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6483,7 +6867,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6544,7 +6932,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6605,7 +6997,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6666,7 +7062,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6727,7 +7127,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6788,7 +7192,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6849,7 +7257,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6910,7 +7322,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6971,7 +7387,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7032,7 +7452,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7093,7 +7517,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7154,7 +7582,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7215,7 +7647,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7276,7 +7712,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7337,7 +7777,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7398,7 +7842,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7459,7 +7907,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7520,7 +7972,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7581,7 +8037,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7642,7 +8102,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7703,7 +8167,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7764,7 +8232,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7825,7 +8297,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7886,7 +8362,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7947,7 +8427,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8008,7 +8492,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8069,7 +8557,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8130,7 +8622,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8191,7 +8687,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8252,7 +8752,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8313,7 +8817,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8374,7 +8882,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8435,7 +8947,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8496,7 +9012,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8557,7 +9077,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8618,7 +9142,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8679,7 +9207,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8740,7 +9272,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8801,7 +9337,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8862,7 +9402,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8923,7 +9467,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8984,7 +9532,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9045,7 +9597,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9106,7 +9662,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9167,7 +9727,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9228,7 +9792,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9289,7 +9857,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9350,7 +9922,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9411,7 +9987,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9472,7 +10052,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9533,7 +10117,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9594,7 +10182,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/pasajes-aereos-nacionales/nuble.xlsx
+++ b/docs/oc-regiones/pasajes-aereos-nacionales/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M150"/>
+  <dimension ref="A1:M151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7664,7 +7664,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1208103-25-CM26</t>
+          <t>1393-279-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7684,17 +7684,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7704,12 +7704,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>363.69</v>
+        <v>580.45</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1393-279-CM26</t>
+          <t>1208103-25-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7749,17 +7749,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7788,7 +7788,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>580.45</v>
+        <v>363.69</v>
       </c>
     </row>
     <row r="114">
@@ -8379,7 +8379,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2705-1225-CM26</t>
+          <t>2705-1227-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>58.17</v>
+        <v>102.69</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2705-1227-CM26</t>
+          <t>2705-1225-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>102.69</v>
+        <v>58.17</v>
       </c>
     </row>
     <row r="125">
@@ -9094,7 +9094,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1049242-53-CM26</t>
+          <t>1049242-52-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9153,13 +9153,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1209.54</v>
+        <v>806.36</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1059240-42-CM26</t>
+          <t>1049242-53-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>62.000.430-8</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -9218,13 +9218,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>790.05</v>
+        <v>1209.54</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1049242-52-CM26</t>
+          <t>1059240-42-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>62.000.430-8</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9283,18 +9283,18 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>806.36</v>
+        <v>790.05</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1059240-44-CM26</t>
+          <t>1059240-43-SE26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2239-16-LR23</t>
+          <t>2239-23-LP10</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -9348,13 +9348,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>435.34</v>
+        <v>61</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1059240-47-CM26</t>
+          <t>1059240-44-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -9413,13 +9413,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>65.59</v>
+        <v>435.34</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1059240-48-CM26</t>
+          <t>1059240-47-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9478,13 +9478,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>140.28</v>
+        <v>65.59</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1059240-50-CM26</t>
+          <t>1059240-48-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -9543,13 +9543,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>258.04</v>
+        <v>140.28</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1700-89-CM26</t>
+          <t>1059240-50-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9608,13 +9608,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>183.03</v>
+        <v>258.04</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1700-90-CM26</t>
+          <t>1700-89-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -9673,13 +9673,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>94.56999999999999</v>
+        <v>183.03</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1059240-52-CM26</t>
+          <t>1700-90-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -9738,13 +9738,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>235.56</v>
+        <v>94.56999999999999</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1059240-53-CM26</t>
+          <t>1059240-52-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9803,13 +9803,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>161.39</v>
+        <v>235.56</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1700-91-CM26</t>
+          <t>1059240-53-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9834,12 +9834,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9868,13 +9868,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>175.77</v>
+        <v>161.39</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2705-1538-CM26</t>
+          <t>1700-91-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9889,22 +9889,22 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9933,13 +9933,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>376.42</v>
+        <v>175.77</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1059109-95-CM26</t>
+          <t>2705-1538-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9954,22 +9954,22 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9998,13 +9998,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>229.76</v>
+        <v>376.42</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2705-1543-CM26</t>
+          <t>1059109-95-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10024,17 +10024,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -10044,12 +10044,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -10063,13 +10063,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>113.98</v>
+        <v>229.76</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2705-1540-CM26</t>
+          <t>2705-1543-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10128,71 +10128,136 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>111.32</v>
+        <v>113.98</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
+          <t>2705-1540-CM26</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>60.911.006-6</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>JetSMART</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>111.32</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
           <t>1059240-59-CM26</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D151" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="E151" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
+      <c r="F151" t="inlineStr">
         <is>
           <t>61.935.400-1</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
+      <c r="G151" t="inlineStr">
         <is>
           <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M150" s="2" t="n">
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="n">
         <v>278.8</v>
       </c>
     </row>

--- a/docs/oc-regiones/pasajes-aereos-nacionales/nuble.xlsx
+++ b/docs/oc-regiones/pasajes-aereos-nacionales/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M151"/>
+  <dimension ref="A1:M165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1424,7 +1424,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2705-539-CM25</t>
+          <t>2705-540-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>391.08</v>
+        <v>163.06</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2705-540-CM25</t>
+          <t>2705-539-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1529,12 +1529,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>163.06</v>
+        <v>391.08</v>
       </c>
     </row>
     <row r="18">
@@ -1749,7 +1749,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1208103-16-CM25</t>
+          <t>1039043-51-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1808,13 +1808,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>390.27</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1039043-51-CM25</t>
+          <t>1059240-23-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1834,17 +1834,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>35.48</v>
+        <v>219.38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1059240-23-CM25</t>
+          <t>1208103-16-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>219.38</v>
+        <v>390.27</v>
       </c>
     </row>
     <row r="24">
@@ -2529,7 +2529,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1208103-33-CM25</t>
+          <t>1059240-37-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2549,17 +2549,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>229.42</v>
+        <v>181.05</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1208103-34-CM25</t>
+          <t>1208103-33-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>467.8</v>
+        <v>229.42</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1059240-37-CM25</t>
+          <t>1208103-34-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2679,17 +2679,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2718,7 +2718,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>181.05</v>
+        <v>467.8</v>
       </c>
     </row>
     <row r="36">
@@ -2919,7 +2919,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1060500-37-CM25</t>
+          <t>1059109-165-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>62.000.510-k</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2978,13 +2978,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>84.61</v>
+        <v>171.28</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1059109-165-CM25</t>
+          <t>3673-388-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3004,17 +3004,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3043,13 +3043,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>171.28</v>
+        <v>1611.74</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3673-388-CM25</t>
+          <t>3673-389-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3108,13 +3108,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1611.74</v>
+        <v>1469.02</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3673-389-CM25</t>
+          <t>1060500-37-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3134,17 +3134,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>62.000.510-k</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3173,7 +3173,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1469.02</v>
+        <v>84.61</v>
       </c>
     </row>
     <row r="43">
@@ -3504,7 +3504,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1059240-51-CM25</t>
+          <t>1059240-50-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3563,13 +3563,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>597.27</v>
+        <v>68.02</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1059240-52-CM25</t>
+          <t>1059240-51-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3628,13 +3628,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>125.75</v>
+        <v>597.27</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1059240-53-CM25</t>
+          <t>1059240-52-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3693,13 +3693,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>216.85</v>
+        <v>125.75</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1059240-50-CM25</t>
+          <t>1059240-53-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3758,13 +3758,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>68.02</v>
+        <v>216.85</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1208103-43-CM25</t>
+          <t>1208103-42-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3823,13 +3823,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>76</v>
+        <v>59.56</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1208103-42-CM25</t>
+          <t>1208103-43-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3888,7 +3888,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>59.56</v>
+        <v>76</v>
       </c>
     </row>
     <row r="54">
@@ -4479,7 +4479,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1049242-92-CM25</t>
+          <t>1049242-90-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4538,13 +4538,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>449.8</v>
+        <v>210.75</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1049242-90-CM25</t>
+          <t>1049242-92-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>210.75</v>
+        <v>449.8</v>
       </c>
     </row>
     <row r="65">
@@ -5129,7 +5129,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1208103-53-CM25</t>
+          <t>1059240-70-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5149,17 +5149,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5188,13 +5188,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>647.37</v>
+        <v>317.97</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1059240-70-CM25</t>
+          <t>1208103-52-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5214,17 +5214,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5253,13 +5253,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>317.97</v>
+        <v>436.05</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1208103-52-CM25</t>
+          <t>1208103-53-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5318,13 +5318,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>436.05</v>
+        <v>647.37</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2705-1573-CM25</t>
+          <t>2705-1570-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5383,13 +5383,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>454.7</v>
+        <v>380.82</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2705-1570-CM25</t>
+          <t>2705-1573-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5448,7 +5448,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>380.82</v>
+        <v>454.7</v>
       </c>
     </row>
     <row r="78">
@@ -6754,7 +6754,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1059240-10-CM26</t>
+          <t>1700-19-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6813,13 +6813,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>867.22</v>
+        <v>700.38</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1700-19-CM26</t>
+          <t>1059240-10-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>700.38</v>
+        <v>867.22</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1700-21-CM26</t>
+          <t>1700-20-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6943,13 +6943,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>122.32</v>
+        <v>69.13</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1700-20-CM26</t>
+          <t>1700-21-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6989,12 +6989,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -7008,7 +7008,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>69.13</v>
+        <v>122.32</v>
       </c>
     </row>
     <row r="102">
@@ -7339,7 +7339,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>4121-38-CM26</t>
+          <t>1049242-29-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7359,17 +7359,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>62.000.430-8</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7398,13 +7398,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>302.78</v>
+        <v>160.52</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1049242-27-CM26</t>
+          <t>1049242-28-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7463,13 +7463,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>188.24</v>
+        <v>198.94</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1049242-28-CM26</t>
+          <t>1049242-27-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7528,13 +7528,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>198.94</v>
+        <v>188.24</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1049242-29-CM26</t>
+          <t>4121-38-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7554,17 +7554,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>62.000.430-8</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -7593,13 +7593,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>160.52</v>
+        <v>302.78</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1347775-9-CM26</t>
+          <t>1393-279-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7619,17 +7619,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7658,13 +7658,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>363.69</v>
+        <v>580.45</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1393-279-CM26</t>
+          <t>1208103-25-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7684,17 +7684,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7704,12 +7704,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>580.45</v>
+        <v>363.69</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1208103-25-CM26</t>
+          <t>1347775-9-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8704,7 +8704,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1173805-20-CM26</t>
+          <t>1173805-21-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -8763,13 +8763,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>210.31</v>
+        <v>300.92</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1173805-21-CM26</t>
+          <t>1173805-20-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8809,12 +8809,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>300.92</v>
+        <v>210.31</v>
       </c>
     </row>
     <row r="130">
@@ -8964,7 +8964,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1049242-50-CM26</t>
+          <t>1700-86-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>62.000.430-8</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -9023,13 +9023,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>194.98</v>
+        <v>157.65</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1700-86-CM26</t>
+          <t>1049242-50-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9054,12 +9054,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>62.000.430-8</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -9069,12 +9069,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -9088,7 +9088,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>157.65</v>
+        <v>194.98</v>
       </c>
     </row>
     <row r="134">
@@ -9159,7 +9159,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1049242-53-CM26</t>
+          <t>1059240-42-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>62.000.430-8</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -9218,13 +9218,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1209.54</v>
+        <v>790.05</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1059240-42-CM26</t>
+          <t>1049242-53-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>62.000.430-8</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>790.05</v>
+        <v>1209.54</v>
       </c>
     </row>
     <row r="137">
@@ -9419,7 +9419,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1059240-47-CM26</t>
+          <t>1059240-48-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9478,13 +9478,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>65.59</v>
+        <v>140.28</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1059240-48-CM26</t>
+          <t>1059240-47-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9543,7 +9543,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>140.28</v>
+        <v>65.59</v>
       </c>
     </row>
     <row r="141">
@@ -9614,7 +9614,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1700-89-CM26</t>
+          <t>1700-90-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -9673,13 +9673,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>183.03</v>
+        <v>94.56999999999999</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1700-90-CM26</t>
+          <t>1700-89-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -9738,13 +9738,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>94.56999999999999</v>
+        <v>183.03</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1059240-52-CM26</t>
+          <t>1700-91-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>235.56</v>
+        <v>175.77</v>
       </c>
     </row>
     <row r="145">
@@ -9874,7 +9874,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1700-91-CM26</t>
+          <t>1059240-52-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>175.77</v>
+        <v>235.56</v>
       </c>
     </row>
     <row r="147">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -10069,7 +10069,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2705-1543-CM26</t>
+          <t>2705-1540-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10128,13 +10128,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>113.98</v>
+        <v>111.32</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2705-1540-CM26</t>
+          <t>2705-1543-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -10193,7 +10193,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>111.32</v>
+        <v>113.98</v>
       </c>
     </row>
     <row r="151">
@@ -10259,6 +10259,916 @@
       </c>
       <c r="M151" s="2" t="n">
         <v>278.8</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>1700-94-CM26</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="n">
+        <v>186.26</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2705-1619-CM26</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>60.911.006-6</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="n">
+        <v>139.85</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>1700-97-CM26</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="n">
+        <v>443.08</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2705-1627-CM26</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>60.911.006-6</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>JetSMART</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="n">
+        <v>46.44</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2705-1629-CM26</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>60.911.006-6</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>JetSMART</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="n">
+        <v>72.28</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>1059240-65-CM26</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="n">
+        <v>214.25</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2705-1635-CM26</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>60.911.006-6</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>JetSMART</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="n">
+        <v>68.38</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2705-1636-CM26</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>60.911.006-6</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>JetSMART</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="n">
+        <v>78.63</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>1051765-918-CM26</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>62.000.570-3</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="n">
+        <v>869.9</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2705-1713-CM26</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>60.911.006-6</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>JetSMART</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="n">
+        <v>121.22</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2705-1721-CM26</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>60.911.006-6</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>JetSMART</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="n">
+        <v>117.76</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>1040538-53-CM26</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>60.704.000-1</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE TURISMO</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="n">
+        <v>90.88</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2705-1747-CM26</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>60.911.006-6</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="n">
+        <v>193.4</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>1043030-86-CM26</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>62.000.480-4</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="n">
+        <v>143.03</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/pasajes-aereos-nacionales/nuble.xlsx
+++ b/docs/oc-regiones/pasajes-aereos-nacionales/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M165"/>
+  <dimension ref="A1:M166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3959,7 +3959,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1700-85-CM25</t>
+          <t>1049242-69-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3979,17 +3979,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>62.000.430-8</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4018,13 +4018,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>115.61</v>
+        <v>173.05</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1049242-69-CM25</t>
+          <t>1700-85-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4044,17 +4044,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>62.000.430-8</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>173.05</v>
+        <v>115.61</v>
       </c>
     </row>
     <row r="57">
@@ -6754,7 +6754,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1700-19-CM26</t>
+          <t>1059240-10-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6813,13 +6813,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>700.38</v>
+        <v>867.22</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1059240-10-CM26</t>
+          <t>1700-19-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>867.22</v>
+        <v>700.38</v>
       </c>
     </row>
     <row r="100">
@@ -7274,7 +7274,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1039043-44-CM26</t>
+          <t>1049242-27-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>62.000.430-8</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7314,12 +7314,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -7333,13 +7333,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>267.92</v>
+        <v>188.24</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1049242-29-CM26</t>
+          <t>1049242-28-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7398,13 +7398,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>160.52</v>
+        <v>198.94</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1049242-28-CM26</t>
+          <t>1049242-29-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -7463,13 +7463,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>198.94</v>
+        <v>160.52</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1049242-27-CM26</t>
+          <t>4121-38-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7489,17 +7489,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>62.000.430-8</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7509,12 +7509,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7528,13 +7528,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>188.24</v>
+        <v>302.78</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>4121-38-CM26</t>
+          <t>1039043-44-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7554,17 +7554,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7593,7 +7593,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>302.78</v>
+        <v>267.92</v>
       </c>
     </row>
     <row r="111">
@@ -9094,7 +9094,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1049242-52-CM26</t>
+          <t>1049242-53-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9153,7 +9153,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>806.36</v>
+        <v>1209.54</v>
       </c>
     </row>
     <row r="135">
@@ -9224,7 +9224,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1049242-53-CM26</t>
+          <t>1049242-52-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1209.54</v>
+        <v>806.36</v>
       </c>
     </row>
     <row r="137">
@@ -10654,7 +10654,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2705-1635-CM26</t>
+          <t>2705-1636-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10713,13 +10713,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>68.38</v>
+        <v>78.63</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2705-1636-CM26</t>
+          <t>2705-1635-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>78.63</v>
+        <v>68.38</v>
       </c>
     </row>
     <row r="160">
@@ -11169,6 +11169,71 @@
       </c>
       <c r="M165" s="2" t="n">
         <v>143.03</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2705-1771-CM26</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>60.911.006-6</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="n">
+        <v>255</v>
       </c>
     </row>
   </sheetData>
